--- a/Architecture.xlsx
+++ b/Architecture.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kazuh\OneDrive\デスクトップ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kazuh\OneDrive\デスクトップ\remoterepos\aws-ecs-fargate-sample-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6D816F-3744-46BC-AA92-156511E30134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30C0ACE-30CD-47D5-8244-E771317A74D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1903,8 +1903,8 @@
       <xdr:rowOff>44823</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>104</xdr:col>
-      <xdr:colOff>130885</xdr:colOff>
+      <xdr:col>105</xdr:col>
+      <xdr:colOff>6195</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>98724</xdr:rowOff>
     </xdr:to>
@@ -2726,6 +2726,214 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>83127</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>19627</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>55418</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 34" descr="Security group.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47B92DF8-E23D-FF72-CB34-F44DFA773D39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2618509" y="4045527"/>
+          <a:ext cx="1765300" cy="2563091"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875">
+          <a:solidFill>
+            <a:srgbClr val="DD344C"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" tIns="91440" anchorCtr="1"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US"/>
+          </a:defPPr>
+          <a:lvl1pPr algn="l" rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0">
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="0"/>
+            </a:spcAft>
+            <a:defRPr kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0">
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="0"/>
+            </a:spcAft>
+            <a:defRPr kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0">
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="0"/>
+            </a:spcAft>
+            <a:defRPr kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0">
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="0"/>
+            </a:spcAft>
+            <a:defRPr kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" rtl="0" eaLnBrk="0" fontAlgn="base" hangingPunct="0">
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="0"/>
+            </a:spcAft>
+            <a:defRPr kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr eaLnBrk="1" fontAlgn="auto" hangingPunct="1">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Security group</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
